--- a/backend/elderlycare-common/src/main/resources/excel_model/ResponsibleArea.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/ResponsibleArea.xlsx
@@ -442,12 +442,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,11 +460,6 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -478,11 +472,6 @@
           <t>remark</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -495,11 +484,6 @@
           <t>自理老人护理区</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -512,11 +496,6 @@
           <t>失能老人专护区</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -527,11 +506,6 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>术后康复护理区</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
         </is>
       </c>
     </row>
